--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -683,12 +683,165 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>结束日期，单日查询时与date相同</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>interval</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dateType</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>lastSrcChannelId1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>groupType</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>skuId</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>attributes</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>skuId</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sortField</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jdr_sch_traffic_enter_shop__browse_page_cnt_shop_last_src</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sortType</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>limit</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>商品流量来源</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>compareType</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hb</t>
         </is>
       </c>
     </row>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>商品搜索效果</t>
+          <t>商品流量来源</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>商品搜索效果</t>
+          <t>商品流量来源</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>商品搜索效果</t>
+          <t>商品流量来源</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>商品搜索效果</t>
+          <t>商品流量来源</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -708,6 +708,11 @@
           <t>DAY</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>时间粒度：DAY=按天汇总，MONTH=按月汇总</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -725,6 +730,11 @@
           <t>day</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>日期类型：day=按日查询（与interval的DAY对应）</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -742,6 +752,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>一级渠道ID：2=商品流量来源（搜索/推荐/购物车均属此类）</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -759,6 +774,11 @@
           <t>skuId</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>聚合维度：skuId=按商品SKU维度汇总数据</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -776,6 +796,11 @@
           <t>skuId</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>返回字段：skuId=仅返回SKU维度的数据列</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -793,6 +818,11 @@
           <t>jdr_sch_traffic_enter_shop__browse_page_cnt_shop_last_src</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>排序字段：按商品入店浏览量降序排序</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -810,6 +840,11 @@
           <t>desc</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>排序方式：desc=降序（浏览量从高到低）</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -827,6 +862,11 @@
           <t>5000</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>返回条数上限：最多导出5000条SKU记录</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,6 +882,11 @@
       <c r="C20" t="inlineStr">
         <is>
           <t>hb</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>对比方式：hb=环比（与上一周期对比）</t>
         </is>
       </c>
     </row>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -744,149 +744,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lastSrcChannelId1</t>
+          <t>limit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>一级渠道ID：2=商品流量来源（搜索/推荐/购物车均属此类）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>groupType</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>skuId</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>聚合维度：skuId=按商品SKU维度汇总数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>attributes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>skuId</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>返回字段：skuId=仅返回SKU维度的数据列</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>sortField</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>jdr_sch_traffic_enter_shop__browse_page_cnt_shop_last_src</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>排序字段：按商品入店浏览量降序排序</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sortType</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>排序方式：desc=降序（浏览量从高到低）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>limit</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
           <t>返回条数上限：最多导出5000条SKU记录</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>商品流量来源</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>compareType</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>hb</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>对比方式：hb=环比（与上一周期对比）</t>
         </is>
       </c>
     </row>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -2,41 +2,193 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="全局配置" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" calcMode="manual" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="23">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="微软雅黑"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -45,12 +197,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -59,14 +397,265 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -77,8 +666,56 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -431,7 +1068,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -441,8 +1077,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -450,7 +1086,7 @@
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>项目名</t>
@@ -472,7 +1108,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>全局</t>
@@ -494,7 +1130,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>全局</t>
@@ -516,7 +1152,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="16.5" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>全局</t>
@@ -538,7 +1174,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>全局</t>
@@ -549,62 +1185,60 @@
           <t>请求间隔(秒)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>两次API调用之间的最小间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>最大重试次数</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>请求失败时的最大重试次数</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>请求超时(秒)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>两次API调用之间的最小间隔</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>全局</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>最大重试次数</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>请求失败时的最大重试次数</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>全局</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>请求超时(秒)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>单次请求的超时时间</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="33" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>商品流量来源</t>
@@ -626,7 +1260,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>商品流量来源</t>
@@ -648,7 +1282,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>商品流量来源</t>
@@ -670,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>商品流量来源</t>
@@ -755,6 +1389,160 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>返回条数上限：最多导出5000条SKU记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cookie文件路径</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>config/jzt_cookie.txt</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>京准通专用Cookie文件（与商智cookie.txt隔离，jzt.jd.com Cookie不互通）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>模板文件路径</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>config/jzt_report_template.json</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>京准通自定义报表JSON模板（外置，__DATE__为日期占位符）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>业务子目录</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>业务子目录名（AGENTS.md Excel规则4）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>轮询间隔(秒)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>轮询报表状态专用间隔（区别于全局请求间隔30s）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>最大轮询次数</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>轮询报表状态最大次数（60次×10秒≈10分钟）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>创建接口URL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://jzt-api.jd.com/dataCenter/customreport/v2/report/add?businessFrom=1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>京准通创建报表接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>京准通自定义报表</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>轮询接口URL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://atoms-api.jd.com/api/download/common/asyn/download/reportInfo/list</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>京准通异步下载状态轮询接口</t>
         </is>
       </c>
     </row>

--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="全局配置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全局配置" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" calcMode="manual" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>config/cookie.txt</t>
+          <t>config/sz_cookie.txt</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
